--- a/Copilot_O365_NL/excel_oefeningen.xlsx
+++ b/Copilot_O365_NL/excel_oefeningen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://quanthicsbv-my.sharepoint.com/personal/thomas_janssen_quanthics_com/Documents/00. QUANTHICS BV/06. Python Scripts/Training_Material/Copilot_O365_NL/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A899A85-2EE8-4782-ADBB-B2F06544059A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facturen" sheetId="3" r:id="rId1"/>
@@ -699,10 +699,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
